--- a/graficos/LDA_mejores_dominio.xlsx
+++ b/graficos/LDA_mejores_dominio.xlsx
@@ -97,25 +97,25 @@
     <t>comisión_lim_dictamen_dom_K35_-</t>
   </si>
   <si>
-    <t>todos_dictamen_dom_K23_-</t>
-  </si>
-  <si>
-    <t>todos_dictamen_dom_K22_-</t>
-  </si>
-  <si>
-    <t>todos_dictamen_dom_K27_-</t>
-  </si>
-  <si>
-    <t>comisión_lim_dictamen_dom_K25_-</t>
+    <t>comisión_lim_dictamen_dom_K23_-</t>
+  </si>
+  <si>
+    <t>todos_dictamen_dom_K20_-</t>
+  </si>
+  <si>
+    <t>todos_dictamen_dom_K24_-</t>
   </si>
   <si>
     <t>todos_dictamen_dom_K15_-</t>
   </si>
   <si>
-    <t>comisión_lim_dictamen_dom_K26_-</t>
-  </si>
-  <si>
     <t>orps_lim_dictamen_dom_K28_-</t>
+  </si>
+  <si>
+    <t>comisión_lim_dictamen_dom_K33_-</t>
+  </si>
+  <si>
+    <t>orps_lim_dictamen_dom_K31_-</t>
   </si>
   <si>
     <t>orps_lim_dictamen_dom_K34_-</t>
@@ -911,7 +911,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>11</v>
@@ -926,19 +926,19 @@
         <v>27</v>
       </c>
       <c r="F14" s="3">
-        <v>0.4869565217391305</v>
+        <v>0.4695652173913044</v>
       </c>
       <c r="G14" s="3">
-        <v>-2.389563826927386</v>
+        <v>-2.401672471055889</v>
       </c>
       <c r="H14" s="2">
         <v>13</v>
       </c>
       <c r="I14" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J14" s="3">
-        <v>0.08724832214765101</v>
+        <v>0.08843537414965986</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -949,7 +949,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>12</v>
@@ -958,19 +958,19 @@
         <v>28</v>
       </c>
       <c r="F15" s="3">
-        <v>0.4545454545454545</v>
+        <v>0.43</v>
       </c>
       <c r="G15" s="3">
-        <v>-2.158114199889732</v>
+        <v>-1.564665079602337</v>
       </c>
       <c r="H15" s="2">
         <v>13</v>
       </c>
       <c r="I15" s="2">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="J15" s="3">
-        <v>0.09352517985611511</v>
+        <v>0.1065573770491803</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -981,7 +981,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>12</v>
@@ -990,30 +990,30 @@
         <v>29</v>
       </c>
       <c r="F16" s="3">
-        <v>0.4296296296296296</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="G16" s="3">
-        <v>-1.517970060723468</v>
+        <v>-1.570966331680821</v>
       </c>
       <c r="H16" s="2">
         <v>13</v>
       </c>
       <c r="I16" s="2">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="J16" s="3">
-        <v>0.08176100628930817</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>12</v>
@@ -1022,30 +1022,30 @@
         <v>30</v>
       </c>
       <c r="F17" s="3">
-        <v>0.396</v>
+        <v>0.3933333333333333</v>
       </c>
       <c r="G17" s="3">
-        <v>-1.984200595476375</v>
+        <v>-1.1872567640398</v>
       </c>
       <c r="H17" s="2">
         <v>13</v>
       </c>
       <c r="I17" s="2">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="J17" s="3">
-        <v>0.08843537414965986</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>12</v>
@@ -1054,19 +1054,19 @@
         <v>31</v>
       </c>
       <c r="F18" s="3">
-        <v>0.3933333333333333</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="G18" s="3">
-        <v>-1.1872567640398</v>
+        <v>-1.422568303864727</v>
       </c>
       <c r="H18" s="2">
         <v>13</v>
       </c>
       <c r="I18" s="2">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="J18" s="3">
-        <v>0.1428571428571428</v>
+        <v>0.08724832214765101</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1077,7 +1077,7 @@
         <v>11</v>
       </c>
       <c r="C19" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>12</v>
@@ -1086,19 +1086,19 @@
         <v>32</v>
       </c>
       <c r="F19" s="3">
-        <v>0.3846153846153846</v>
+        <v>0.2848484848484849</v>
       </c>
       <c r="G19" s="3">
-        <v>-1.591906978429102</v>
+        <v>-1.940769089110694</v>
       </c>
       <c r="H19" s="2">
         <v>13</v>
       </c>
       <c r="I19" s="2">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="J19" s="3">
-        <v>0.08609271523178808</v>
+        <v>0.07647058823529412</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1109,7 +1109,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>12</v>
@@ -1118,19 +1118,19 @@
         <v>33</v>
       </c>
       <c r="F20" s="3">
-        <v>0.3392857142857143</v>
+        <v>0.2709677419354839</v>
       </c>
       <c r="G20" s="3">
-        <v>-1.422568303864727</v>
+        <v>-2.07433751178252</v>
       </c>
       <c r="H20" s="2">
         <v>13</v>
       </c>
       <c r="I20" s="2">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="J20" s="3">
-        <v>0.08724832214765101</v>
+        <v>0.09285714285714286</v>
       </c>
     </row>
     <row r="21" spans="1:10">
